--- a/InputData/trans/FoSfBPPTtC/Fraction of Subsidy for Battery Production Passed Through to Consumers.xlsx
+++ b/InputData/trans/FoSfBPPTtC/Fraction of Subsidy for Battery Production Passed Through to Consumers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28706"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\FoSfBPPTtC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\trans\FoSfBPPTtC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C42E453D-9834-499C-8AB7-6F5D5B5F88BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55C0FA4B-8005-4A60-95CE-CB331902CA86}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DF91DE-8113-4B26-9104-BCC4B1BA574A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="2100" windowWidth="21600" windowHeight="12735" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="31935" yWindow="3675" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,9 +131,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -171,7 +171,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -277,7 +277,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -419,7 +419,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -428,17 +428,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="101.28515625" customWidth="1"/>
+    <col min="2" max="2" width="101.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -446,27 +446,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
     </row>
   </sheetData>
@@ -479,108 +479,111 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="1" max="1" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="30">
+    <row r="2" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -672,6 +675,9 @@
         <v>0</v>
       </c>
       <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
         <v>0</v>
       </c>
     </row>
@@ -825,12 +831,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -839,14 +839,43 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09B69D56-322E-4F3A-A68B-BBA5ACCA9425}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09B69D56-322E-4F3A-A68B-BBA5ACCA9425}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C3C8875-1F5E-4931-81B4-1804B696537E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96AA02D2-2833-4007-9AC3-526505D8FF58}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96AA02D2-2833-4007-9AC3-526505D8FF58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C3C8875-1F5E-4931-81B4-1804B696537E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>